--- a/data_extactor/batch_10_fa/trimmed/batch_0067_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0067_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری | رایانه و الکترونیک | ریاضیات | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | رایانه و الکترونیک | ریاضیات | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کارشناسان خدمات مشتریان | مصاحبه‌گران تعیین صلاحیت برنامه‌های دولتی | متخصصان اطلاعات سلامت و ثبت داده‌های پزشکی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | متخصصان منابع انسانی | متصدیان امور دفتری، عمومی | متصدیان پذیرش و اطلاعات</t>
+          <t>کارشناسان خدمات و پشتیبانی مشتریان | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | کارشناسان منابع انسانی | متصدیان امور دفتری و امور عمومی اداری | متصدیان پذیرش و اطلاعات</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | امور اداری | زبان انگلیسی | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | اداری | زبان انگلیسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان شفاهی | مرتب‌سازی اطلاعات | درک شفاهی | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی</t>
+          <t>درک کتبی | بیان شفاهی | ترتیب‌دهی اطلاعات | درک شفاهی | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>آرشیوپژوهان و کارشناسان اسناد تاریخی | متخصصان مدیریت اسناد | متصدیان بایگانی | کتابداران و متخصصان مجموعه‌های چندرسانه‌ای | تکنسین‌های کتابداری | متصدیان امور دفتری، عمومی | متصدیان پذیرش و اطلاعات</t>
+          <t>کارشناسان اسناد و آرشیو | کارشناسان مدیریت اسناد و مدارک | متصدیان بایگانی و اسناد | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | تکنسین‌های کتابداری | متصدیان امور دفتری و امور عمومی اداری | متصدیان پذیرش و اطلاعات</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری | رایانه و الکترونیک | حقوق و امور دولتی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | رایانه و الکترونیک | قانون و دولت | ریاضیات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال ریاضی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ماموران وصول مطالبات و حساب‌ها | کارشناسان دفترداری، حسابداری و حسابرسی | تحلیل‌گران اعتبار | متصدیان بررسی، تایید و پرونده‌های اعتبار | کارشناسان اعطای تسهیلات | کارشناسان افتتاح حساب | تحویل‌داران</t>
+          <t>کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان دفترداری، حسابداری و امور حسابرسی | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان و مسئولان تسهیلات و اعتبارات | متصدیان افتتاح حساب | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | فروش و بازاریابی | امور اداری | رایانه و الکترونیک | ریاضیات | اقتصاد و حسابداری</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | اداری | رایانه و الکترونیک | ریاضیات | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | تشخیص گفتار | استدلال قیاسی | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | تشخیص گفتار | استدلال قیاسی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کارشناسان صدور صورت‌حساب و ثبت اسناد | کارشناسان دفترداری، حسابداری و حسابرسی | کارشناسان خدمات مشتریان | نمایندگان فروش بیمه | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان اعطای تسهیلات | تحویل‌داران</t>
+          <t>کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان خدمات و پشتیبانی مشتریان | نمایندگان و کارشناسان فروش بیمه | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان و مسئولان تسهیلات و اعتبارات | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | تولید و فرآوری | رایانه و الکترونیک | امور اداری | ریاضیات | فروش و بازاریابی | حمل‌ونقل</t>
+          <t>خدمات مشتری و شخصی | تولید و فرآوری | رایانه و الکترونیک | اداری | ریاضیات | فروش و بازاریابی | حمل و نقل</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دید نزدیک | تشخیص گفتار | درک شفاهی | بیان شفاهی | درک کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>بینایی نزدیک | تشخیص گفتار | درک شفاهی | بیان شفاهی | درک کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارشناسان صدور صورت‌حساب و ثبت اسناد | کارشناسان خدمات مشتریان | متصدیان امور دفتری، عمومی | کارشناسان تدارکات و خرید | کارشناسان برنامه‌ریزی، تولید و پیگیری | کارمندان بارگیری، تحویل‌گیری و انبارداری | کارگران چیدمان و آماده‌سازی سفارش</t>
+          <t>کارمندان صدور صورتحساب و ثبت اسناد مالی | کارشناسان خدمات و پشتیبانی مشتریان | متصدیان امور دفتری و امور عمومی اداری | کارمندان تدارکات و کارپردازی | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارمندان انبار، ارسال و دریافت کالا | متصدیان چیدمان و آماده‌سازی سفارش</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | نگارش | نظارت | تفکر انتقادی | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | نظارت | تفکر انتقادی | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پرسنلی و منابع انسانی | امور اداری | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | زبان انگلیسی</t>
+          <t>پرسنل و منابع انسانی | اداری | خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | متخصصان جبران خدمت، مزایا و تجزیه و تحلیل شغل | منشی‌ها و دستیاران اجرایی مدیریت | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | مدیران منابع انسانی | متخصصان منابع انسانی | کارشناسان حقوق، دستمزد و ثبت ساعات کار</t>
+          <t>مدیران خدمات اداری و پشتیبانی | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | مسئولان دفاتر و دستیاران اجرایی مدیریت | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | مدیران منابع انسانی | کارشناسان منابع انسانی | کارمندان امور حقوق، دستمزد و ثبت زمان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | امور اداری | زبان انگلیسی | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | اداری | زبان انگلیسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کارشناسان خدمات مشتریان | منشی‌ها و دستیاران اجرایی مدیریت | متصدیان بایگانی | متصدیان پذیرش هتل، متل و اقامتگاه | متصدیان امور دفتری، عمومی | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | اپراتورهای تلفنخانه، شامل خدمات پاسخ‌گویی</t>
+          <t>کارشناسان خدمات و پشتیبانی مشتریان | مسئولان دفاتر و دستیاران اجرایی مدیریت | متصدیان بایگانی و اسناد | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | متصدیان امور دفتری و امور عمومی اداری | منشی‌ها و دستیاران اداری عمومی | اپراتورهای مراکز تلفن و پاسخگویی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | رایانه و الکترونیک | ایمنی و امنیت عمومی | حمل‌ونقل | جغرافیا | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | ایمنی و امنیت عمومی | حمل و نقل | جغرافیا | روان‌شناسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک شفاهی | درک کتبی | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کارشناسان خدمات مشتریان | دیسپچرهای ناوگان حمل‌ونقل، به جز پلیس، آتش‌نشانی و اورژانس | مهمانداران هواپیما | متصدیان پذیرش هتل، متل و اقامتگاه | متصدیان پذیرش و اطلاعات | مدیران فنی و دفاتر خدمات مسافرتی | راهنمایان تور و گردشگری</t>
+          <t>کارشناسان خدمات و پشتیبانی مشتریان | متصدیان دیسپاچ و اعزام | مهمانداران هواپیما | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | متصدیان پذیرش و اطلاعات | کارشناسان و دفاتر خدمات مسافرتی و جهانگردی | راهنمایان گردشگری و تور</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | مدیریت و امور اداری | رایانه و الکترونیک | حقوق و امور دولتی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | قانون و دولت | ریاضیات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | درک کتبی | توجه انتخابی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک کتبی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>متصدیان بایگانی | کارشناسان مکاتبات اداری | متصدیان ثبت و پیگیری سفارش‌ها | متصدیان پذیرش و اطلاعات | کارشناسان خدمات مشتریان | اپراتورهای ورود اطلاعات | متصدیان امور دفتری، عمومی</t>
+          <t>متصدیان بایگانی و اسناد | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | متصدیان ثبت و پیگیری سفارش‌ها | متصدیان پذیرش و اطلاعات | کارشناسان خدمات و پشتیبانی مشتریان | متصدیان ورود اطلاعات و داده‌آمایی | متصدیان امور دفتری و امور عمومی اداری</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | درک مطلب | نظارت | نگارش</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | جغرافیا | ایمنی و امنیت عمومی | مدیریت و امور اداری | حقوق و امور دولتی | امور اداری | خدمات مشتریان و خدمات فردی</t>
+          <t>حمل و نقل | جغرافیا | ایمنی و امنیت عمومی | مدیریت و اداره | قانون و دولت | اداری | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کارگزاران گمرکی (حق‌العمل‌کاران گمرک) | دیسپچرهای ناوگان حمل‌ونقل، به جز پلیس، آتش‌نشانی و اورژانس | کارگزاران ترابری و حمل‌ونقل کالا (فورواردری) | کارشناسان ارشد لجستیک | تحلیل‌گران لجستیک و زنجیره تامین | متصدیان ثبت و پیگیری سفارش‌ها | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>حق‌العمل‌کاران و کارگزاران گمرکی | متصدیان دیسپاچ و اعزام | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | کارشناسان لجستیک و مدیریت زنجیره تأمین | تحلیل‌گران لجستیک و فرایند توزیع | متصدیان ثبت و پیگیری سفارش‌ها | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
